--- a/1-LATEX/2-DADOS/3-OUTPUT/tabela_ISB_consolidada.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/tabela_ISB_consolidada.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -419,22 +419,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vulnerabilidade Jurídica</t>
+          <t>Exposicao Climatica</t>
         </is>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D2">
-        <v>-0.2787297834861159</v>
+        <v>0.2796759127099698</v>
       </c>
       <c r="E2">
-        <v>-24.3</v>
+        <v>32.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -442,45 +442,45 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.471</v>
+        <v>0.34</v>
       </c>
       <c r="H2">
-        <v>30.68844264259262</v>
+        <v>9.09172822407833E-09</v>
       </c>
       <c r="I2">
-        <v>0.1706084965332423</v>
+        <v>4.655057934973063E-10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Estreita</t>
         </is>
       </c>
       <c r="K2">
-        <v>-39</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
-        <v>-6.1</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Organização Social</t>
+          <t>Vulnerabilidade Juridica</t>
         </is>
       </c>
       <c r="C3">
         <v>37</v>
       </c>
       <c r="D3">
-        <v>0.1716000516464709</v>
+        <v>-0.2787297834861159</v>
       </c>
       <c r="E3">
-        <v>18.7</v>
+        <v>-24.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -488,45 +488,45 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.29</v>
+        <v>0.339</v>
       </c>
       <c r="H3">
-        <v>8.40253021833796</v>
+        <v>30.68844264259262</v>
       </c>
       <c r="I3">
-        <v>0.101150822222562</v>
+        <v>0.1706084965332423</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Estreita</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="K3">
-        <v>-5.3</v>
+        <v>-39</v>
       </c>
       <c r="L3">
-        <v>48.9</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Singularidade Territorial</t>
+          <t>Organizacao Social</t>
         </is>
       </c>
       <c r="C4">
         <v>37</v>
       </c>
       <c r="D4">
-        <v>0.0715762333288117</v>
+        <v>0.1716000516464709</v>
       </c>
       <c r="E4">
-        <v>7.4</v>
+        <v>18.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.121</v>
+        <v>0.209</v>
       </c>
       <c r="H4">
-        <v>6.074724194413331</v>
+        <v>8.40253021833796</v>
       </c>
       <c r="I4">
-        <v>0.02766083366641499</v>
+        <v>0.101150822222562</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -548,31 +548,31 @@
         </is>
       </c>
       <c r="K4">
-        <v>-8.6</v>
+        <v>-5.3</v>
       </c>
       <c r="L4">
-        <v>26.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Complexidade Biocultural</t>
+          <t>Integracao ao Mercado</t>
         </is>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>0.04486936865596249</v>
+        <v>0.05120757691971459</v>
       </c>
       <c r="E5">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.076</v>
+        <v>0.062</v>
       </c>
       <c r="H5">
-        <v>2.438881119934042</v>
+        <v>3.484765520565583E-08</v>
       </c>
       <c r="I5">
-        <v>0.02121684598240538</v>
+        <v>2.050008407799427E-09</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="K5">
-        <v>-6.5</v>
+        <v>-0.9</v>
       </c>
       <c r="L5">
-        <v>17</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erosão Intergeracional</t>
+          <t>Erosao Intergeracional</t>
         </is>
       </c>
       <c r="C6">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="H6">
         <v>14.8053164203369</v>
@@ -649,47 +649,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Status de Documentação</t>
+          <t>Complexidade Biocultural</t>
         </is>
       </c>
       <c r="C7">
         <v>37</v>
       </c>
       <c r="D7">
+        <v>0.01655094282820235</v>
+      </c>
+      <c r="E7">
+        <v>1.7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0.02</v>
+      </c>
+      <c r="H7">
+        <v>3.642037642435129</v>
+      </c>
+      <c r="I7">
+        <v>0.02389601709455585</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Estreita</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="L7">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Status de Documentacao</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>37</v>
+      </c>
+      <c r="D8">
         <v>0.007406689765167936</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>0.7</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Confirmatória (meta-análise completa)</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0.013</v>
-      </c>
-      <c r="H7">
+      <c r="G8">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H8">
         <v>7.629654219477611</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>0.09260327465062979</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Estreita</t>
         </is>
       </c>
-      <c r="K7">
+      <c r="K8">
         <v>-18.9</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>25.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vitalidade Linguistica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>47</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Confirmatória (meta-análise completa)</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>4.849856232471125E-08</v>
+      </c>
+      <c r="I9">
+        <v>2.991635273407584E-09</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Estreita</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
